--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_29_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_29_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1727,10 +1727,10 @@
         <v>11</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3105,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>2</v>
@@ -3497,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -3827,16 +3827,16 @@
         <v>69</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>21</v>
@@ -4488,10 +4488,10 @@
         <v>27</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4684,10 +4684,10 @@
         <v>16</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
         <v>5</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5272,16 +5272,16 @@
         <v>11</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>4</v>
@@ -5471,13 +5471,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>4</v>
@@ -5664,16 +5664,16 @@
         <v>19</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>5</v>
@@ -6056,7 +6056,7 @@
         <v>8</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>126</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U48" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X48" t="n">
         <v>34</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_29_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_29_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
         <v>9</v>
@@ -692,20 +692,20 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>37.50</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,58 +1739,58 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3111,14 +3111,14 @@
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3503,14 +3503,14 @@
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,10 +5676,10 @@
         <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>5</v>
       </c>
       <c r="X48" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="Y48" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="AA48" t="n">
